--- a/Python_3Month_Coding_Tracker.xlsx
+++ b/Python_3Month_Coding_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9122d646c0a87bf/Shamreen/ML/ML Job Hunt/Python-90DaysChallenge/-90DaysOfPythonChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE52713A-D1CC-42E0-9B8E-471B84808B4C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2502DB5F-5B26-4CEA-9CEB-39C016869F59}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -686,6 +686,9 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -699,6 +702,9 @@
       </c>
       <c r="D4" t="s">
         <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">

--- a/Python_3Month_Coding_Tracker.xlsx
+++ b/Python_3Month_Coding_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9122d646c0a87bf/Shamreen/ML/ML Job Hunt/Python-90DaysChallenge/-90DaysOfPythonChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2502DB5F-5B26-4CEA-9CEB-39C016869F59}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03F962BC-4962-4E0C-8F91-23CD72A6D30E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -720,6 +720,9 @@
       <c r="D5" t="s">
         <v>8</v>
       </c>
+      <c r="E5" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">

--- a/Python_3Month_Coding_Tracker.xlsx
+++ b/Python_3Month_Coding_Tracker.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9122d646c0a87bf/Shamreen/ML/ML Job Hunt/Python-90DaysChallenge/-90DaysOfPythonChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03F962BC-4962-4E0C-8F91-23CD72A6D30E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A5FF39B-670A-4CF5-A72D-3AE2CA310074}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Python Coding Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -737,6 +737,9 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -751,6 +754,9 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -765,6 +771,9 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -778,6 +787,9 @@
       </c>
       <c r="D9" t="s">
         <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">

--- a/Python_3Month_Coding_Tracker.xlsx
+++ b/Python_3Month_Coding_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9122d646c0a87bf/Shamreen/ML/ML Job Hunt/Python-90DaysChallenge/-90DaysOfPythonChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A5FF39B-670A-4CF5-A72D-3AE2CA310074}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DC3228F-7D3A-4B6F-AA42-682A86D70B4C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -805,6 +805,9 @@
       <c r="D10" t="s">
         <v>8</v>
       </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -818,6 +821,9 @@
       </c>
       <c r="D11" t="s">
         <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">

--- a/Python_3Month_Coding_Tracker.xlsx
+++ b/Python_3Month_Coding_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9122d646c0a87bf/Shamreen/ML/ML JH/Python-90DaysChallenge/-90DaysOfPythonChallenge/-90DaysOfPythonChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A613CB75-3947-4B4D-B28E-7363C0FCDD12}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{3DBD0F8E-6C9B-4A91-8047-102BBB268D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15A76AB7-F5AB-4DB7-B6B7-C7FB4C23FEAF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -703,6 +703,9 @@
       <c r="D4" t="s">
         <v>8</v>
       </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -716,6 +719,9 @@
       </c>
       <c r="D5" t="s">
         <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
